--- a/Analisis de materias.xlsx
+++ b/Analisis de materias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redanahuac-my.sharepoint.com/personal/jesus_ramosb_anahuac_mx/Documents/Escritorio/Dashboard materias/Gemini/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{AEC493ED-2EAA-4A63-B3CF-5A8E4EB94C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18205EF8-9B57-4A38-807C-645FC73F8846}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{AEC493ED-2EAA-4A63-B3CF-5A8E4EB94C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{696B188E-57C2-44BB-B137-A88CF40F5277}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="1155" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="251">
   <si>
     <t>Curso</t>
   </si>
@@ -3449,6 +3449,12 @@
       <c r="M45" s="3" t="s">
         <v>118</v>
       </c>
+      <c r="U45" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="46" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
@@ -5348,7 +5354,7 @@
       </c>
       <c r="U85">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V85">
         <f t="shared" si="0"/>
@@ -5372,7 +5378,7 @@
       </c>
       <c r="AA85">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -5402,6 +5408,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100746788ECA2CB6D4CABE5D7502D755DCA" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b557a76437666cee21a6f69402bf685b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="479396de-7aa0-4d05-b479-200d7d9b7401" xmlns:ns3="b20dacbb-42f0-4102-8766-afa36f399016" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d57372443af83b9b55e9c442ea9b760" ns2:_="" ns3:_="">
     <xsd:import namespace="479396de-7aa0-4d05-b479-200d7d9b7401"/>
@@ -5602,15 +5617,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97211F9D-8E6C-4C4A-9609-0BFEA02706C2}">
   <ds:schemaRefs>
@@ -5623,6 +5629,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C93DBCD-9347-4844-9B25-FDDBE47EDF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710B5ED4-CD15-4957-8C89-0E007DD9DB57}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5639,12 +5653,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C93DBCD-9347-4844-9B25-FDDBE47EDF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>